--- a/00_output/35_Feasibility_Inputs.xlsx
+++ b/00_output/35_Feasibility_Inputs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://nv5inc-my.sharepoint.com/personal/andrewj_johnson_nv5_com/Documents/Documents/GitHub/Potential_Study_Tool_Prototype/00_output/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="11_A9B03BAC5B66E2CFEB3B98154B7606BCA3E8B32C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E122938E-C081-4B81-BF78-BC5B6EA48574}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="11_A9B03BAC5B66E2CFEB3B98154B7606BCA3E8B32C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A93C01EA-56CD-4CB9-8B1E-84DCF8AC308E}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-3420" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -420,8 +420,8 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="63.7109375" customWidth="1"/>
-    <col min="2" max="2" width="18.7109375" customWidth="1"/>
-    <col min="3" max="3" width="11.140625" customWidth="1"/>
+    <col min="2" max="2" width="26.28515625" customWidth="1"/>
+    <col min="3" max="3" width="27.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">

--- a/00_output/35_Feasibility_Inputs.xlsx
+++ b/00_output/35_Feasibility_Inputs.xlsx
@@ -1,106 +1,55 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://nv5inc-my.sharepoint.com/personal/andrewj_johnson_nv5_com/Documents/Documents/GitHub/Potential_Study_Tool_Prototype/00_output/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="11_A9B03BAC5B66E2CFEB3B98154B7606BCA3E8B32C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A93C01EA-56CD-4CB9-8B1E-84DCF8AC308E}"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-3420" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="feasibility" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="feasibility" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="19">
-  <si>
-    <t>measure_name</t>
-  </si>
-  <si>
-    <t>competition_group</t>
-  </si>
-  <si>
-    <t>efficiency_level</t>
-  </si>
-  <si>
-    <t>single_family_feasibility</t>
-  </si>
-  <si>
-    <t>multifamily_feasibility</t>
-  </si>
-  <si>
-    <t>single_family_li_feasibility</t>
-  </si>
-  <si>
-    <t>multifamily_li_feasibility</t>
-  </si>
-  <si>
-    <t>existing_to_furnace_oil_efficient_residential_1</t>
-  </si>
-  <si>
-    <t>heating_cooling</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>existing_to_furnace_oil_efficient_residential_2</t>
-  </si>
-  <si>
-    <t>existing_to_furnace_natural_gas_efficient_residential_1</t>
-  </si>
-  <si>
-    <t>existing_to_furnace_natural_gas_efficient_residential_2</t>
-  </si>
-  <si>
-    <t>baseline_to_refrigerator_electric_efficient_residential</t>
-  </si>
-  <si>
-    <t>refrigeration</t>
-  </si>
-  <si>
-    <t>baseline_to_refrigerator_electric_top10_residential</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>existing_to_refrigerator_electric_efficient_residential</t>
-  </si>
-  <si>
-    <t>existing_to_refrigerator_electric_top10_residential</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F2F2"/>
+        <bgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -108,26 +57,113 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="00000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="00000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="00000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="00000000"/>
+      </bottom>
+    </border>
+    <border>
+      <bottom style="thin">
+        <color rgb="00D9D9D9"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+  <cellXfs count="6">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -415,127 +451,230 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:G9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="63.7109375" customWidth="1"/>
-    <col min="2" max="2" width="26.28515625" customWidth="1"/>
-    <col min="3" max="3" width="27.42578125" customWidth="1"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" t="s">
-        <v>14</v>
-      </c>
-      <c r="C6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7" t="s">
-        <v>14</v>
-      </c>
-      <c r="C7" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>17</v>
-      </c>
-      <c r="B8" t="s">
-        <v>14</v>
-      </c>
-      <c r="C8" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>18</v>
-      </c>
-      <c r="B9" t="s">
-        <v>14</v>
-      </c>
-      <c r="C9" t="s">
-        <v>16</v>
-      </c>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>measure_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>competition_group</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>efficiency_level</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>single_family_feasibility</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>multifamily_feasibility</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>single_family_li_feasibility</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>multifamily_li_feasibility</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>existing_to_furnace_oil_efficient_residential_1a</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>heating_cooling</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="n"/>
+      <c r="E2" s="3" t="n"/>
+      <c r="F2" s="3" t="n"/>
+      <c r="G2" s="3" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>existing_to_furnace_oil_efficient_residential_3b</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>heating_cooling</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="n"/>
+      <c r="E3" s="5" t="n"/>
+      <c r="F3" s="5" t="n"/>
+      <c r="G3" s="5" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>existing_to_furnace_natural_gas_efficient_residential_1a</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>heating_cooling</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="n"/>
+      <c r="E4" s="3" t="n"/>
+      <c r="F4" s="3" t="n"/>
+      <c r="G4" s="3" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>existing_to_furnace_natural_gas_efficient_residential_3b</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>heating_cooling</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="5" t="n"/>
+      <c r="F5" s="5" t="n"/>
+      <c r="G5" s="5" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>baseline_to_refrigerator_electric_efficient_residential</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>refrigeration</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="n"/>
+      <c r="E6" s="3" t="n"/>
+      <c r="F6" s="3" t="n"/>
+      <c r="G6" s="3" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>baseline_to_refrigerator_electric_top10_residential</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>refrigeration</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="n"/>
+      <c r="E7" s="5" t="n"/>
+      <c r="F7" s="5" t="n"/>
+      <c r="G7" s="5" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>existing_to_refrigerator_electric_efficient_residential</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>refrigeration</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="n"/>
+      <c r="E8" s="3" t="n"/>
+      <c r="F8" s="3" t="n"/>
+      <c r="G8" s="3" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>existing_to_refrigerator_electric_top10_residential</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>refrigeration</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="n"/>
+      <c r="E9" s="5" t="n"/>
+      <c r="F9" s="5" t="n"/>
+      <c r="G9" s="5" t="n"/>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/00_output/35_Feasibility_Inputs.xlsx
+++ b/00_output/35_Feasibility_Inputs.xlsx
@@ -459,7 +459,7 @@
   <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="58" customWidth="1" min="1" max="1"/>
     <col width="19" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="27" customWidth="1" min="4" max="4"/>
